--- a/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLÍNICA PONFERRADA SDP.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/aggregate_individual/AGG_IND_CLÍNICA PONFERRADA SDP.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>P. TREVIÑO QUINTILLÁ</t>
+          <t>J. BERGENS</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -562,70 +562,70 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D2" t="n">
-        <v>34.853</v>
+        <v>33.7615</v>
       </c>
       <c r="E2" t="n">
-        <v>28.9763</v>
+        <v>35.3591</v>
       </c>
       <c r="F2" t="n">
-        <v>5.8771</v>
+        <v>-1.5976</v>
       </c>
       <c r="G2" t="n">
-        <v>7.0959</v>
+        <v>18.3299</v>
       </c>
       <c r="H2" t="n">
-        <v>4.398</v>
+        <v>-9.446300000000001</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6983</v>
+        <v>27.7763</v>
       </c>
       <c r="J2" t="n">
-        <v>29.1686</v>
+        <v>46.7385</v>
       </c>
       <c r="K2" t="n">
-        <v>14.7872</v>
+        <v>6.148899999999999</v>
       </c>
       <c r="L2" t="n">
-        <v>14.3812</v>
+        <v>40.5898</v>
       </c>
       <c r="M2" t="n">
-        <v>-22.0722</v>
+        <v>-28.4086</v>
       </c>
       <c r="N2" t="n">
-        <v>-10.3897</v>
+        <v>-15.5952</v>
       </c>
       <c r="O2" t="n">
-        <v>-11.6827</v>
+        <v>-12.8135</v>
       </c>
       <c r="P2" t="n">
-        <v>8.9491</v>
+        <v>-11.2384</v>
       </c>
       <c r="Q2" t="n">
-        <v>-27.0555</v>
+        <v>-47.4512</v>
       </c>
       <c r="R2" t="n">
-        <v>36.0045</v>
+        <v>36.2123</v>
       </c>
       <c r="S2" t="n">
-        <v>16.5792</v>
+        <v>1.6179</v>
       </c>
       <c r="T2" t="n">
-        <v>6.5733</v>
+        <v>-3.2703</v>
       </c>
       <c r="U2" t="n">
-        <v>10.006</v>
+        <v>4.8882</v>
       </c>
       <c r="V2" t="n">
-        <v>2.228800000000001</v>
+        <v>25.0522</v>
       </c>
       <c r="W2" t="n">
-        <v>20.2904</v>
+        <v>39.3421</v>
       </c>
       <c r="X2" t="n">
-        <v>-18.0613</v>
+        <v>-14.2899</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>26</v>
       </c>
       <c r="D3" t="n">
-        <v>21.9773</v>
+        <v>33.6256</v>
       </c>
       <c r="E3" t="n">
-        <v>16.9851</v>
+        <v>25.3295</v>
       </c>
       <c r="F3" t="n">
-        <v>4.992599999999999</v>
+        <v>8.296199999999999</v>
       </c>
       <c r="G3" t="n">
         <v>21.0509</v>
@@ -688,13 +688,13 @@
         <v>35.7964</v>
       </c>
       <c r="S3" t="n">
-        <v>-12.0128</v>
+        <v>-0.3647000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>-14.4767</v>
+        <v>-6.1322</v>
       </c>
       <c r="U3" t="n">
-        <v>2.4634</v>
+        <v>5.7677</v>
       </c>
       <c r="V3" t="n">
         <v>14.3958</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. BERGENS</t>
+          <t>P. TREVIÑO QUINTILLÁ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -718,76 +718,76 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D4" t="n">
-        <v>21.4025</v>
+        <v>26.9964</v>
       </c>
       <c r="E4" t="n">
-        <v>27.7839</v>
+        <v>24.271</v>
       </c>
       <c r="F4" t="n">
-        <v>-6.3814</v>
+        <v>2.7257</v>
       </c>
       <c r="G4" t="n">
-        <v>18.3299</v>
+        <v>7.0959</v>
       </c>
       <c r="H4" t="n">
-        <v>-9.446300000000001</v>
+        <v>4.398</v>
       </c>
       <c r="I4" t="n">
-        <v>27.7763</v>
+        <v>2.6983</v>
       </c>
       <c r="J4" t="n">
-        <v>46.7385</v>
+        <v>29.1686</v>
       </c>
       <c r="K4" t="n">
-        <v>6.148899999999999</v>
+        <v>14.7872</v>
       </c>
       <c r="L4" t="n">
-        <v>40.5898</v>
+        <v>14.3812</v>
       </c>
       <c r="M4" t="n">
-        <v>-28.4086</v>
+        <v>-22.0722</v>
       </c>
       <c r="N4" t="n">
-        <v>-15.5952</v>
+        <v>-10.3897</v>
       </c>
       <c r="O4" t="n">
-        <v>-12.8135</v>
+        <v>-11.6827</v>
       </c>
       <c r="P4" t="n">
-        <v>-11.2384</v>
+        <v>8.9491</v>
       </c>
       <c r="Q4" t="n">
-        <v>-47.4512</v>
+        <v>-27.0555</v>
       </c>
       <c r="R4" t="n">
-        <v>36.2123</v>
+        <v>36.0045</v>
       </c>
       <c r="S4" t="n">
-        <v>-10.7412</v>
+        <v>8.722199999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>-10.8462</v>
+        <v>1.8677</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1047999999999997</v>
+        <v>6.8545</v>
       </c>
       <c r="V4" t="n">
-        <v>25.0522</v>
+        <v>2.228800000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>39.3421</v>
+        <v>20.2904</v>
       </c>
       <c r="X4" t="n">
-        <v>-14.2899</v>
+        <v>-18.0613</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. HAYES</t>
+          <t>N. OKEKE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -796,70 +796,70 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>12.7246</v>
+        <v>10.8591</v>
       </c>
       <c r="E5" t="n">
-        <v>7.746900000000001</v>
+        <v>12.315</v>
       </c>
       <c r="F5" t="n">
-        <v>4.9779</v>
+        <v>-1.4558</v>
       </c>
       <c r="G5" t="n">
-        <v>-14.3399</v>
+        <v>5.2767</v>
       </c>
       <c r="H5" t="n">
-        <v>-9.2897</v>
+        <v>3.047</v>
       </c>
       <c r="I5" t="n">
-        <v>-5.050000000000001</v>
+        <v>2.2297</v>
       </c>
       <c r="J5" t="n">
-        <v>20.2953</v>
+        <v>18.6848</v>
       </c>
       <c r="K5" t="n">
-        <v>9.205100000000002</v>
+        <v>9.299300000000001</v>
       </c>
       <c r="L5" t="n">
-        <v>11.0905</v>
+        <v>9.385399999999999</v>
       </c>
       <c r="M5" t="n">
-        <v>-34.635</v>
+        <v>-13.4081</v>
       </c>
       <c r="N5" t="n">
-        <v>-18.4949</v>
+        <v>-6.2521</v>
       </c>
       <c r="O5" t="n">
-        <v>-16.1405</v>
+        <v>-7.1557</v>
       </c>
       <c r="P5" t="n">
-        <v>-25.3905</v>
+        <v>2.2893</v>
       </c>
       <c r="Q5" t="n">
-        <v>-72.0091</v>
+        <v>-17.6901</v>
       </c>
       <c r="R5" t="n">
-        <v>46.6185</v>
+        <v>19.9793</v>
       </c>
       <c r="S5" t="n">
-        <v>32.8161</v>
+        <v>2.1717</v>
       </c>
       <c r="T5" t="n">
-        <v>19.7646</v>
+        <v>-0.6910999999999999</v>
       </c>
       <c r="U5" t="n">
-        <v>13.0514</v>
+        <v>2.8627</v>
       </c>
       <c r="V5" t="n">
-        <v>19.6392</v>
+        <v>1.1216</v>
       </c>
       <c r="W5" t="n">
-        <v>39.6956</v>
+        <v>12.0115</v>
       </c>
       <c r="X5" t="n">
-        <v>-20.0566</v>
+        <v>-10.8899</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>11.9774</v>
+        <v>10.1984</v>
       </c>
       <c r="E6" t="n">
-        <v>7.9358</v>
+        <v>7.250799999999999</v>
       </c>
       <c r="F6" t="n">
-        <v>4.0417</v>
+        <v>2.9475</v>
       </c>
       <c r="G6" t="n">
         <v>4.9211</v>
@@ -922,13 +922,13 @@
         <v>13.3195</v>
       </c>
       <c r="S6" t="n">
-        <v>5.7835</v>
+        <v>4.0046</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4948</v>
+        <v>-0.1901</v>
       </c>
       <c r="U6" t="n">
-        <v>5.2889</v>
+        <v>4.1947</v>
       </c>
       <c r="V6" t="n">
         <v>-6.2197</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>N. OKEKE</t>
+          <t>D. ORRIT SERRANO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -952,76 +952,76 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="D7" t="n">
-        <v>11.7147</v>
+        <v>4.382</v>
       </c>
       <c r="E7" t="n">
-        <v>14.4347</v>
+        <v>-6.440300000000002</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.7202</v>
+        <v>10.8221</v>
       </c>
       <c r="G7" t="n">
-        <v>5.2767</v>
+        <v>-8.327999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>3.047</v>
+        <v>-13.9474</v>
       </c>
       <c r="I7" t="n">
-        <v>2.2297</v>
+        <v>5.619300000000001</v>
       </c>
       <c r="J7" t="n">
-        <v>18.6848</v>
+        <v>20.122</v>
       </c>
       <c r="K7" t="n">
-        <v>9.299300000000001</v>
+        <v>0.1993000000000005</v>
       </c>
       <c r="L7" t="n">
-        <v>9.385399999999999</v>
+        <v>19.923</v>
       </c>
       <c r="M7" t="n">
-        <v>-13.4081</v>
+        <v>-28.45</v>
       </c>
       <c r="N7" t="n">
-        <v>-6.2521</v>
+        <v>-14.1465</v>
       </c>
       <c r="O7" t="n">
-        <v>-7.1557</v>
+        <v>-14.3034</v>
       </c>
       <c r="P7" t="n">
-        <v>2.2893</v>
+        <v>-15.401</v>
       </c>
       <c r="Q7" t="n">
-        <v>-17.6901</v>
+        <v>-57.8571</v>
       </c>
       <c r="R7" t="n">
-        <v>19.9793</v>
+        <v>42.4559</v>
       </c>
       <c r="S7" t="n">
-        <v>3.027</v>
+        <v>3.1075</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4288</v>
+        <v>-3.9437</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5981</v>
+        <v>7.0509</v>
       </c>
       <c r="V7" t="n">
-        <v>1.1216</v>
+        <v>25.0029</v>
       </c>
       <c r="W7" t="n">
-        <v>12.0115</v>
+        <v>35.2381</v>
       </c>
       <c r="X7" t="n">
-        <v>-10.8899</v>
+        <v>-10.2353</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. CHACON CARNERO</t>
+          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1030,76 +1030,76 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>1.1399</v>
+        <v>1.814</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2719</v>
+        <v>3.5574</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.132</v>
+        <v>-1.7435</v>
       </c>
       <c r="G8" t="n">
-        <v>1.3681</v>
+        <v>4.3879</v>
       </c>
       <c r="H8" t="n">
-        <v>1.0873</v>
+        <v>2.1966</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2808</v>
+        <v>2.1913</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8988</v>
+        <v>7.5479</v>
       </c>
       <c r="K8" t="n">
-        <v>0.9077999999999999</v>
+        <v>3.5115</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.009000000000000036</v>
+        <v>4.0364</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4693000000000001</v>
+        <v>-3.1599</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1795</v>
+        <v>-1.3147</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2898000000000001</v>
+        <v>-1.8451</v>
       </c>
       <c r="P8" t="n">
-        <v>0.4162</v>
+        <v>-1.4568</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.2487</v>
+        <v>-4.1624</v>
       </c>
       <c r="R8" t="n">
-        <v>1.6649</v>
+        <v>2.7056</v>
       </c>
       <c r="S8" t="n">
-        <v>3.3358</v>
+        <v>0.2803</v>
       </c>
       <c r="T8" t="n">
-        <v>2.0995</v>
+        <v>0.1719</v>
       </c>
       <c r="U8" t="n">
-        <v>1.2364</v>
+        <v>0.1084</v>
       </c>
       <c r="V8" t="n">
-        <v>-3.9803</v>
+        <v>-1.3975</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.4776</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-3.5026</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. LÓPEZ ÁLVAREZ-TIRADOR</t>
+          <t>J. CHACON CARNERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1108,70 +1108,70 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4630000000000002</v>
+        <v>-0.6452</v>
       </c>
       <c r="E9" t="n">
-        <v>2.3788</v>
+        <v>-0.01389999999999958</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.9159</v>
+        <v>-0.6312</v>
       </c>
       <c r="G9" t="n">
-        <v>4.3879</v>
+        <v>1.3681</v>
       </c>
       <c r="H9" t="n">
-        <v>2.1966</v>
+        <v>1.0873</v>
       </c>
       <c r="I9" t="n">
-        <v>2.1913</v>
+        <v>0.2808</v>
       </c>
       <c r="J9" t="n">
-        <v>7.5479</v>
+        <v>0.8988</v>
       </c>
       <c r="K9" t="n">
-        <v>3.5115</v>
+        <v>0.9077999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>4.0364</v>
+        <v>-0.009000000000000036</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.1599</v>
+        <v>0.4693000000000001</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3147</v>
+        <v>0.1795</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.8451</v>
+        <v>0.2898000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.4568</v>
+        <v>0.4162</v>
       </c>
       <c r="Q9" t="n">
-        <v>-4.1624</v>
+        <v>-1.2487</v>
       </c>
       <c r="R9" t="n">
-        <v>2.7056</v>
+        <v>1.6649</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.0705</v>
+        <v>1.5508</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.0067</v>
+        <v>0.8135</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.064</v>
+        <v>0.7375</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3975</v>
+        <v>-3.9803</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.4776</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.3975</v>
+        <v>-3.5026</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>2</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.8123</v>
+        <v>-0.6949</v>
       </c>
       <c r="E10" t="n">
         <v>-0.5026999999999999</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3096</v>
+        <v>-0.1922</v>
       </c>
       <c r="G10" t="n">
         <v>-0.434</v>
@@ -1234,13 +1234,13 @@
         <v>0.2081</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5866</v>
+        <v>-0.4691</v>
       </c>
       <c r="T10" t="n">
         <v>-0.5219</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.06459999999999999</v>
+        <v>0.0529</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,13 +1267,13 @@
         <v>4</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.2907</v>
+        <v>-1.4501</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4667</v>
+        <v>-3.9373</v>
       </c>
       <c r="F11" t="n">
-        <v>2.176</v>
+        <v>2.4871</v>
       </c>
       <c r="G11" t="n">
         <v>-2.9804</v>
@@ -1312,13 +1312,13 @@
         <v>4.7867</v>
       </c>
       <c r="S11" t="n">
-        <v>1.5992</v>
+        <v>1.4397</v>
       </c>
       <c r="T11" t="n">
-        <v>0.5367999999999999</v>
+        <v>0.0663</v>
       </c>
       <c r="U11" t="n">
-        <v>1.0622</v>
+        <v>1.3734</v>
       </c>
       <c r="V11" t="n">
         <v>-1.5744</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>C. KNOWLES</t>
+          <t>R. BLAK MOLLER</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1342,76 +1342,76 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9722</v>
+        <v>-1.7453</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.308300000000001</v>
+        <v>-11.8194</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.6639999999999998</v>
+        <v>10.0739</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.059900000000001</v>
+        <v>-17.243</v>
       </c>
       <c r="H12" t="n">
-        <v>2.6166</v>
+        <v>0.8564000000000003</v>
       </c>
       <c r="I12" t="n">
-        <v>-4.676399999999999</v>
+        <v>-18.0996</v>
       </c>
       <c r="J12" t="n">
-        <v>1.0347</v>
+        <v>1.1923</v>
       </c>
       <c r="K12" t="n">
-        <v>2.5475</v>
+        <v>6.8743</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.5128</v>
+        <v>-5.681900000000001</v>
       </c>
       <c r="M12" t="n">
-        <v>-3.0947</v>
+        <v>-18.4353</v>
       </c>
       <c r="N12" t="n">
-        <v>0.06910000000000005</v>
+        <v>-6.0177</v>
       </c>
       <c r="O12" t="n">
-        <v>-3.1636</v>
+        <v>-12.4174</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2082000000000002</v>
+        <v>24.9743</v>
       </c>
       <c r="Q12" t="n">
-        <v>-4.1624</v>
+        <v>-16.2333</v>
       </c>
       <c r="R12" t="n">
-        <v>3.9542</v>
+        <v>41.2074</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3068</v>
+        <v>1.4982</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.4105</v>
+        <v>-3.005</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1038</v>
+        <v>4.5033</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.3974</v>
+        <v>-10.9747</v>
       </c>
       <c r="W12" t="n">
-        <v>0.23</v>
+        <v>6.2267</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.6274</v>
+        <v>-17.2014</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>J. LARREA IBARBURU</t>
+          <t>C. KNOWLES</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1420,76 +1420,76 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D13" t="n">
-        <v>-5.0054</v>
+        <v>-2.5402</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.6112</v>
+        <v>-2.6356</v>
       </c>
       <c r="F13" t="n">
-        <v>1.6057</v>
+        <v>0.09549999999999992</v>
       </c>
       <c r="G13" t="n">
-        <v>0.04389999999999994</v>
+        <v>-2.059900000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>1.1982</v>
+        <v>2.6166</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.1544</v>
+        <v>-4.676399999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-1.0134</v>
+        <v>1.0347</v>
       </c>
       <c r="K13" t="n">
-        <v>0.3942000000000001</v>
+        <v>2.5475</v>
       </c>
       <c r="L13" t="n">
-        <v>-1.4076</v>
+        <v>-1.5128</v>
       </c>
       <c r="M13" t="n">
-        <v>1.0572</v>
+        <v>-3.0947</v>
       </c>
       <c r="N13" t="n">
-        <v>0.8041</v>
+        <v>0.06910000000000005</v>
       </c>
       <c r="O13" t="n">
-        <v>0.2530999999999999</v>
+        <v>-3.1636</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.5381</v>
+        <v>-0.2082000000000002</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.202999999999999</v>
+        <v>-4.1624</v>
       </c>
       <c r="R13" t="n">
-        <v>1.6649</v>
+        <v>3.9542</v>
       </c>
       <c r="S13" t="n">
-        <v>0.24</v>
+        <v>1.1252</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.3947</v>
+        <v>0.2619</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6348999999999999</v>
+        <v>0.8634000000000001</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.7513</v>
+        <v>-1.3974</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.7513</v>
+        <v>-1.6274</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. MORALES ROS</t>
+          <t>J. LARREA IBARBURU</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1498,76 +1498,76 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="D14" t="n">
-        <v>-5.111699999999998</v>
+        <v>-5.0832</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1876</v>
+        <v>-6.7183</v>
       </c>
       <c r="F14" t="n">
-        <v>-9.299099999999999</v>
+        <v>1.6351</v>
       </c>
       <c r="G14" t="n">
-        <v>-11.4091</v>
+        <v>0.04389999999999994</v>
       </c>
       <c r="H14" t="n">
-        <v>-4.9944</v>
+        <v>1.1982</v>
       </c>
       <c r="I14" t="n">
-        <v>-6.414800000000001</v>
+        <v>-1.1544</v>
       </c>
       <c r="J14" t="n">
-        <v>6.9594</v>
+        <v>-1.0134</v>
       </c>
       <c r="K14" t="n">
-        <v>5.4468</v>
+        <v>0.3942000000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>1.5126</v>
+        <v>-1.4076</v>
       </c>
       <c r="M14" t="n">
-        <v>-18.3685</v>
+        <v>1.0572</v>
       </c>
       <c r="N14" t="n">
-        <v>-10.4409</v>
+        <v>0.8041</v>
       </c>
       <c r="O14" t="n">
-        <v>-7.9272</v>
+        <v>0.2530999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>12.2791</v>
+        <v>-3.5381</v>
       </c>
       <c r="Q14" t="n">
-        <v>-10.1978</v>
+        <v>-5.202999999999999</v>
       </c>
       <c r="R14" t="n">
-        <v>22.4767</v>
+        <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>10.5408</v>
+        <v>0.1623</v>
       </c>
       <c r="T14" t="n">
-        <v>7.1429</v>
+        <v>-0.5019</v>
       </c>
       <c r="U14" t="n">
-        <v>3.3978</v>
+        <v>0.6642</v>
       </c>
       <c r="V14" t="n">
-        <v>-16.5224</v>
+        <v>-1.7513</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2829999999999998</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>-16.8054</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>D. ORRIT SERRANO</t>
+          <t>S. ROMERO SANCHEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1576,76 +1576,76 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" t="n">
-        <v>-5.978599999999998</v>
+        <v>-5.385100000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>-14.356</v>
+        <v>-1.3468</v>
       </c>
       <c r="F15" t="n">
-        <v>8.377299999999998</v>
+        <v>-4.0379</v>
       </c>
       <c r="G15" t="n">
-        <v>-8.327999999999999</v>
+        <v>-1.834800000000002</v>
       </c>
       <c r="H15" t="n">
-        <v>-13.9474</v>
+        <v>-6.3028</v>
       </c>
       <c r="I15" t="n">
-        <v>5.619300000000001</v>
+        <v>4.468299999999999</v>
       </c>
       <c r="J15" t="n">
-        <v>20.122</v>
+        <v>16.7102</v>
       </c>
       <c r="K15" t="n">
-        <v>0.1993000000000005</v>
+        <v>3.7598</v>
       </c>
       <c r="L15" t="n">
-        <v>19.923</v>
+        <v>12.9508</v>
       </c>
       <c r="M15" t="n">
-        <v>-28.45</v>
+        <v>-18.5446</v>
       </c>
       <c r="N15" t="n">
-        <v>-14.1465</v>
+        <v>-10.0624</v>
       </c>
       <c r="O15" t="n">
-        <v>-14.3034</v>
+        <v>-8.4825</v>
       </c>
       <c r="P15" t="n">
-        <v>-15.401</v>
+        <v>17.274</v>
       </c>
       <c r="Q15" t="n">
-        <v>-57.8571</v>
+        <v>-16.4414</v>
       </c>
       <c r="R15" t="n">
-        <v>42.4559</v>
+        <v>33.7154</v>
       </c>
       <c r="S15" t="n">
-        <v>-7.2529</v>
+        <v>-2.4589</v>
       </c>
       <c r="T15" t="n">
-        <v>-11.8593</v>
+        <v>-2.2879</v>
       </c>
       <c r="U15" t="n">
-        <v>4.606599999999999</v>
+        <v>-0.1707000000000002</v>
       </c>
       <c r="V15" t="n">
-        <v>25.0029</v>
+        <v>-18.3655</v>
       </c>
       <c r="W15" t="n">
-        <v>35.2381</v>
+        <v>0.6721999999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>-10.2353</v>
+        <v>-19.0378</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R. BLAK MOLLER</t>
+          <t>R. HAYES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1654,76 +1654,76 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D16" t="n">
-        <v>-8.254999999999999</v>
+        <v>-6.725199999999999</v>
       </c>
       <c r="E16" t="n">
-        <v>-12.6628</v>
+        <v>-8.3169</v>
       </c>
       <c r="F16" t="n">
-        <v>4.4077</v>
+        <v>1.5914</v>
       </c>
       <c r="G16" t="n">
-        <v>-17.243</v>
+        <v>-14.3399</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8564000000000003</v>
+        <v>-9.2897</v>
       </c>
       <c r="I16" t="n">
-        <v>-18.0996</v>
+        <v>-5.050000000000001</v>
       </c>
       <c r="J16" t="n">
-        <v>1.1923</v>
+        <v>20.2953</v>
       </c>
       <c r="K16" t="n">
-        <v>6.8743</v>
+        <v>9.205100000000002</v>
       </c>
       <c r="L16" t="n">
-        <v>-5.681900000000001</v>
+        <v>11.0905</v>
       </c>
       <c r="M16" t="n">
-        <v>-18.4353</v>
+        <v>-34.635</v>
       </c>
       <c r="N16" t="n">
-        <v>-6.0177</v>
+        <v>-18.4949</v>
       </c>
       <c r="O16" t="n">
-        <v>-12.4174</v>
+        <v>-16.1405</v>
       </c>
       <c r="P16" t="n">
-        <v>24.9743</v>
+        <v>-25.3905</v>
       </c>
       <c r="Q16" t="n">
-        <v>-16.2333</v>
+        <v>-72.0091</v>
       </c>
       <c r="R16" t="n">
-        <v>41.2074</v>
+        <v>46.6185</v>
       </c>
       <c r="S16" t="n">
-        <v>-5.0116</v>
+        <v>13.3658</v>
       </c>
       <c r="T16" t="n">
-        <v>-3.8484</v>
+        <v>3.7006</v>
       </c>
       <c r="U16" t="n">
-        <v>-1.1628</v>
+        <v>9.665100000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>-10.9747</v>
+        <v>19.6392</v>
       </c>
       <c r="W16" t="n">
-        <v>6.2267</v>
+        <v>39.6956</v>
       </c>
       <c r="X16" t="n">
-        <v>-17.2014</v>
+        <v>-20.0566</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>A. MORALES ROS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1732,76 +1732,76 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="D17" t="n">
-        <v>-15.2712</v>
+        <v>-10.0333</v>
       </c>
       <c r="E17" t="n">
-        <v>-13.4599</v>
+        <v>-0.5225000000000009</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8113</v>
+        <v>-9.5105</v>
       </c>
       <c r="G17" t="n">
-        <v>-7.0099</v>
+        <v>-11.4091</v>
       </c>
       <c r="H17" t="n">
-        <v>-3.0723</v>
+        <v>-4.9944</v>
       </c>
       <c r="I17" t="n">
-        <v>-3.9376</v>
+        <v>-6.414800000000001</v>
       </c>
       <c r="J17" t="n">
-        <v>1.9803</v>
+        <v>6.9594</v>
       </c>
       <c r="K17" t="n">
-        <v>1.1663</v>
+        <v>5.4468</v>
       </c>
       <c r="L17" t="n">
-        <v>0.8140999999999999</v>
+        <v>1.5126</v>
       </c>
       <c r="M17" t="n">
-        <v>-8.9902</v>
+        <v>-18.3685</v>
       </c>
       <c r="N17" t="n">
-        <v>-4.2387</v>
+        <v>-10.4409</v>
       </c>
       <c r="O17" t="n">
-        <v>-4.751399999999999</v>
+        <v>-7.9272</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.7462</v>
+        <v>12.2791</v>
       </c>
       <c r="Q17" t="n">
-        <v>-15.6089</v>
+        <v>-10.1978</v>
       </c>
       <c r="R17" t="n">
-        <v>11.8627</v>
+        <v>22.4767</v>
       </c>
       <c r="S17" t="n">
-        <v>4.6589</v>
+        <v>5.619</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0358</v>
+        <v>2.4329</v>
       </c>
       <c r="U17" t="n">
-        <v>3.6233</v>
+        <v>3.1865</v>
       </c>
       <c r="V17" t="n">
-        <v>-9.1738</v>
+        <v>-16.5224</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.8669</v>
+        <v>0.2829999999999998</v>
       </c>
       <c r="X17" t="n">
-        <v>-8.307</v>
+        <v>-16.8054</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>S. ROMERO SANCHEZ</t>
+          <t>O. SIMA FATTY</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>25</v>
       </c>
       <c r="D18" t="n">
-        <v>-17.9585</v>
+        <v>-15.9785</v>
       </c>
       <c r="E18" t="n">
-        <v>-9.174000000000001</v>
+        <v>-22.0183</v>
       </c>
       <c r="F18" t="n">
-        <v>-8.7845</v>
+        <v>6.0401</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.834800000000002</v>
+        <v>-20.6593</v>
       </c>
       <c r="H18" t="n">
-        <v>-6.3028</v>
+        <v>-11.8148</v>
       </c>
       <c r="I18" t="n">
-        <v>4.468299999999999</v>
+        <v>-8.8444</v>
       </c>
       <c r="J18" t="n">
-        <v>16.7102</v>
+        <v>-10.6099</v>
       </c>
       <c r="K18" t="n">
-        <v>3.7598</v>
+        <v>-2.0143</v>
       </c>
       <c r="L18" t="n">
-        <v>12.9508</v>
+        <v>-8.5954</v>
       </c>
       <c r="M18" t="n">
-        <v>-18.5446</v>
+        <v>-10.0494</v>
       </c>
       <c r="N18" t="n">
-        <v>-10.0624</v>
+        <v>-9.800800000000001</v>
       </c>
       <c r="O18" t="n">
-        <v>-8.4825</v>
+        <v>-0.2488999999999998</v>
       </c>
       <c r="P18" t="n">
-        <v>17.274</v>
+        <v>10.8223</v>
       </c>
       <c r="Q18" t="n">
-        <v>-16.4414</v>
+        <v>-14.3602</v>
       </c>
       <c r="R18" t="n">
-        <v>33.7154</v>
+        <v>25.1822</v>
       </c>
       <c r="S18" t="n">
-        <v>-15.0326</v>
+        <v>3.4858</v>
       </c>
       <c r="T18" t="n">
-        <v>-10.1151</v>
+        <v>-3.3279</v>
       </c>
       <c r="U18" t="n">
-        <v>-4.9172</v>
+        <v>6.8139</v>
       </c>
       <c r="V18" t="n">
-        <v>-18.3655</v>
+        <v>-9.626899999999999</v>
       </c>
       <c r="W18" t="n">
-        <v>0.6721999999999999</v>
+        <v>6.28</v>
       </c>
       <c r="X18" t="n">
-        <v>-19.0378</v>
+        <v>-15.907</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. SIMA FATTY</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1888,70 +1888,70 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
-        <v>-17.9782</v>
+        <v>-16.8021</v>
       </c>
       <c r="E19" t="n">
-        <v>-22.8384</v>
+        <v>-14.2702</v>
       </c>
       <c r="F19" t="n">
-        <v>4.8601</v>
+        <v>-2.5319</v>
       </c>
       <c r="G19" t="n">
-        <v>-20.6593</v>
+        <v>-7.0099</v>
       </c>
       <c r="H19" t="n">
-        <v>-11.8148</v>
+        <v>-3.0723</v>
       </c>
       <c r="I19" t="n">
-        <v>-8.8444</v>
+        <v>-3.9376</v>
       </c>
       <c r="J19" t="n">
-        <v>-10.6099</v>
+        <v>1.9803</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.0143</v>
+        <v>1.1663</v>
       </c>
       <c r="L19" t="n">
-        <v>-8.5954</v>
+        <v>0.8140999999999999</v>
       </c>
       <c r="M19" t="n">
-        <v>-10.0494</v>
+        <v>-8.9902</v>
       </c>
       <c r="N19" t="n">
-        <v>-9.800800000000001</v>
+        <v>-4.2387</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2488999999999998</v>
+        <v>-4.751399999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>10.8223</v>
+        <v>-3.7462</v>
       </c>
       <c r="Q19" t="n">
-        <v>-14.3602</v>
+        <v>-15.6089</v>
       </c>
       <c r="R19" t="n">
-        <v>25.1822</v>
+        <v>11.8627</v>
       </c>
       <c r="S19" t="n">
-        <v>1.4854</v>
+        <v>3.128</v>
       </c>
       <c r="T19" t="n">
-        <v>-4.148499999999999</v>
+        <v>0.2250000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>5.6337</v>
+        <v>2.9031</v>
       </c>
       <c r="V19" t="n">
-        <v>-9.626899999999999</v>
+        <v>-9.1738</v>
       </c>
       <c r="W19" t="n">
-        <v>6.28</v>
+        <v>-0.8669</v>
       </c>
       <c r="X19" t="n">
-        <v>-15.907</v>
+        <v>-8.307</v>
       </c>
     </row>
     <row r="20">
@@ -1969,22 +1969,22 @@
         <v>26</v>
       </c>
       <c r="D20" t="n">
-        <v>33.61860000000001</v>
+        <v>54.5539</v>
       </c>
       <c r="E20" t="n">
-        <v>24.32100000000001</v>
+        <v>29.5406</v>
       </c>
       <c r="F20" t="n">
-        <v>9.298099999999998</v>
+        <v>25.014</v>
       </c>
       <c r="G20" t="n">
-        <v>-23.8239</v>
+        <v>-23.82389999999999</v>
       </c>
       <c r="H20" t="n">
         <v>-46.192</v>
       </c>
       <c r="I20" t="n">
-        <v>22.3694</v>
+        <v>22.36939999999999</v>
       </c>
       <c r="J20" t="n">
         <v>207.2724</v>
@@ -2011,19 +2011,19 @@
         <v>-355.8836</v>
       </c>
       <c r="R20" t="n">
-        <v>379.8152</v>
+        <v>379.8152000000001</v>
       </c>
       <c r="S20" t="n">
-        <v>27.0509</v>
+        <v>47.9863</v>
       </c>
       <c r="T20" t="n">
-        <v>-19.5515</v>
+        <v>-14.3322</v>
       </c>
       <c r="U20" t="n">
-        <v>46.6027</v>
+        <v>62.3197</v>
       </c>
       <c r="V20" t="n">
-        <v>6.456599999999998</v>
+        <v>6.456599999999995</v>
       </c>
       <c r="W20" t="n">
         <v>192.4827</v>
